--- a/cargo-pmcp/src/templates/workbook_bundle/template.xlsx
+++ b/cargo-pmcp/src/templates/workbook_bundle/template.xlsx
@@ -611,7 +611,7 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <f>ROUND(B4*G3-1759,0)</f>
+        <f>ROUND(B4*G3-3759,0)</f>
         <v>18241</v>
       </c>
       <c r="C11" t="s">
